--- a/trade-elasticities-cointegration/outputs/section_14_reproducibility_check.xlsx
+++ b/trade-elasticities-cointegration/outputs/section_14_reproducibility_check.xlsx
@@ -555,7 +555,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -623,7 +623,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>series principales clasificadas como I(1)</t>
+          <t>estacionalidad evaluada en primeras diferencias</t>
         </is>
       </c>
       <c r="B5" t="b">
@@ -631,14 +631,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Si algun test individual presenta evidencia mixta, revisar comentarios de la seccion 9.</t>
+          <t>La evaluacion usa Kruskal-Wallis por trimestre como diagnostico simple y complementario.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cointegracion evaluada para importaciones y exportaciones</t>
+          <t>series principales clasificadas como I(1)</t>
         </is>
       </c>
       <c r="B6" t="b">
@@ -646,14 +646,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>La decision ECM se apoya en la evidencia acumulada de Engle-Granger y Gregory-Hansen.</t>
+          <t>Si algun test individual presenta evidencia mixta, revisar comentarios de la seccion 9.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>residuos Engle-Granger incorporados al panel de modelacion</t>
+          <t>cointegracion evaluada para importaciones y exportaciones</t>
         </is>
       </c>
       <c r="B7" t="b">
@@ -661,14 +661,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Los residuos y sus rezagos quedan al final del .dta de modelacion.</t>
+          <t>La decision ECM se apoya en la evidencia acumulada de Engle-Granger y Gregory-Hansen.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>modelos ECM/diferencias estimados y exportados</t>
+          <t>residuos Engle-Granger incorporados al panel de modelacion</t>
         </is>
       </c>
       <c r="B8" t="b">
@@ -676,14 +676,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>La seccion 11 concentra seleccion de rezagos, parsimonia, HAC y sensibilidad.</t>
+          <t>Los residuos y sus rezagos quedan al final del .dta de modelacion.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>diagnosticos post-estimacion sin alertas al 5%</t>
+          <t>modelos ECM/diferencias estimados y exportados</t>
         </is>
       </c>
       <c r="B9" t="b">
@@ -691,14 +691,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Los tests aplicados no detectan autocorrelacion, heterocedasticidad, no normalidad ni inestabilidad al 5%.</t>
+          <t>La seccion 11 concentra seleccion de rezagos, parsimonia, HAC y sensibilidad.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>outputs finales esperados disponibles</t>
+          <t>diagnosticos post-estimacion sin alertas al 5%</t>
         </is>
       </c>
       <c r="B10" t="b">
@@ -706,20 +706,35 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>La seccion 13 no detecta archivos faltantes entre los outputs esperados.</t>
+          <t>Los tests aplicados no detectan autocorrelacion, heterocedasticidad, no normalidad ni inestabilidad al 5%.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>outputs finales esperados disponibles</t>
+        </is>
+      </c>
+      <c r="B11" t="b">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>La seccion 13 no detecta archivos faltantes entre los outputs esperados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>trazabilidad de PIBSOCIOS disponible</t>
         </is>
       </c>
-      <c r="B11" t="b">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B12" t="b">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>PIBSOCIOS queda documentado por ponderadores originales, normalizados, fuente y periodo.</t>
         </is>
@@ -732,7 +747,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -760,7 +775,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>El ADF sobre residuos se reporta con p-values aproximados; la inferencia formal usa valores criticos especificos de cointegracion.</t>
+          <t>El ADF sobre residuos se compara contra la tabla critica Engle-Granger del curso; el p-value estandar queda solo como referencia aproximada.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -885,6 +900,23 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>diagnosticos/anexo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Wickens-Breusch</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>No se implementa estimacion conjunta Wickens-Breusch; los ECM se interpretan como aproximacion estandar de dos etapas.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>limitaciones metodologicas</t>
         </is>
       </c>
     </row>
@@ -950,7 +982,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>46163.87730687833</v>
+        <v>46164.04535139439</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>

--- a/trade-elasticities-cointegration/outputs/section_14_reproducibility_check.xlsx
+++ b/trade-elasticities-cointegration/outputs/section_14_reproducibility_check.xlsx
@@ -982,7 +982,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2">
-        <v>46164.04535139439</v>
+        <v>46164.8059661225</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
